--- a/data/trans_dic/P1408-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1408-Edad-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,59</t>
+          <t>0,57; 2,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,54</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,2</t>
+          <t>0,0; 1,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 7,36</t>
+          <t>0,61; 6,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,37</t>
+          <t>0,36; 1,45</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,72</t>
+          <t>0,0; 0,9</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,96</t>
+          <t>0,28; 3,11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -857,32 +857,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,05</t>
+          <t>0,51; 2,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>0,0; 0,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,02</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,91</t>
+          <t>0,0; 1,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,32</t>
+          <t>0,91; 3,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,0; 0,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,27 +892,27 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,62</t>
+          <t>0,4; 2,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,17</t>
+          <t>0,88; 2,21</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,61</t>
+          <t>0,0; 0,56</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,95</t>
+          <t>0,17; 0,97</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,72</t>
+          <t>0,32; 1,54</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,17</t>
+          <t>0,46; 2,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,57</t>
+          <t>0,28; 1,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,52</t>
+          <t>0,14; 1,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,45</t>
+          <t>0,0; 1,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,76</t>
+          <t>0,77; 2,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,61</t>
+          <t>0,26; 1,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,35</t>
+          <t>0,15; 1,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,38</t>
+          <t>0,14; 1,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,13</t>
+          <t>0,81; 2,08</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,24</t>
+          <t>0,35; 1,31</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,11</t>
+          <t>0,23; 1,05</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,11</t>
+          <t>0,19; 0,98</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,72</t>
+          <t>1,51; 4,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,82</t>
+          <t>0,36; 2,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,26</t>
+          <t>0,49; 2,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,72</t>
+          <t>1,02; 3,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,64</t>
+          <t>1,75; 4,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,03</t>
+          <t>0,18; 2,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,44</t>
+          <t>0,16; 1,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,55</t>
+          <t>1,07; 2,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,02; 4,13</t>
+          <t>1,91; 4,08</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,88</t>
+          <t>0,49; 1,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,49</t>
+          <t>0,47; 1,48</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,22</t>
+          <t>1,2; 2,56</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,27; 9,27</t>
+          <t>4,42; 8,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,96; 6,13</t>
+          <t>2,04; 6,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,68; 6,58</t>
+          <t>2,56; 6,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,96; 4,62</t>
+          <t>2,06; 4,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 4,26</t>
+          <t>1,0; 4,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,73</t>
+          <t>0,96; 3,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,9</t>
+          <t>0,47; 2,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,94; 4,17</t>
+          <t>1,97; 4,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,92; 5,79</t>
+          <t>3,08; 5,76</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,26</t>
+          <t>1,79; 4,25</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,07</t>
+          <t>1,69; 4,01</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,23; 4,02</t>
+          <t>2,37; 4,19</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,43; 14,22</t>
+          <t>7,39; 14,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,53; 9,26</t>
+          <t>3,35; 9,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,32; 6,58</t>
+          <t>2,31; 6,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,7; 8,61</t>
+          <t>4,47; 8,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,63; 8,51</t>
+          <t>3,77; 8,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,41</t>
+          <t>0,58; 3,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,85; 5,84</t>
+          <t>1,81; 5,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,6</t>
+          <t>2,95; 5,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,01; 10,03</t>
+          <t>6,14; 10,25</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,28; 5,25</t>
+          <t>2,16; 5,25</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,35</t>
+          <t>2,48; 5,29</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,77; 5,63</t>
+          <t>4,14; 6,62</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,35; 27,56</t>
+          <t>16,16; 27,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,59; 15,44</t>
+          <t>7,76; 16,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,41; 10,86</t>
+          <t>4,73; 10,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,25; 11,84</t>
+          <t>5,92; 10,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,48; 10,82</t>
+          <t>4,85; 10,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,55; 6,58</t>
+          <t>2,57; 6,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,05; 6,52</t>
+          <t>2,05; 6,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,04; 8,34</t>
+          <t>4,88; 8,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10,28; 15,97</t>
+          <t>9,97; 15,81</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,12; 9,5</t>
+          <t>5,04; 9,1</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,61; 7,21</t>
+          <t>3,56; 7,04</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,0; 8,86</t>
+          <t>5,78; 8,68</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,46; 4,82</t>
+          <t>3,54; 4,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,73</t>
+          <t>1,61; 2,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,46</t>
+          <t>1,53; 2,49</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,82; 2,94</t>
+          <t>2,05; 3,05</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,18; 3,33</t>
+          <t>2,2; 3,28</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,65</t>
+          <t>0,87; 1,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,94; 1,71</t>
+          <t>0,88; 1,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,92; 2,97</t>
+          <t>2,17; 3,06</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,98; 3,9</t>
+          <t>3,0; 3,88</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,37; 1,99</t>
+          <t>1,37; 2,03</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,32; 1,91</t>
+          <t>1,33; 1,91</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,03; 2,84</t>
+          <t>2,2; 2,92</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7969</t>
+          <t>8280</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7969</t>
+          <t>8280</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2784; 12808</t>
+          <t>2792; 12977</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6442</t>
+          <t>0; 7001</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5599</t>
+          <t>0; 5356</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2208; 23045</t>
+          <t>2225; 23538</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3529; 13162</t>
+          <t>3503; 13944</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 5894</t>
+          <t>0; 7310</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2216; 21115</t>
+          <t>2186; 23952</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5476</t>
+          <t>5532</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7812</t>
+          <t>7912</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3757; 15080</t>
+          <t>3760; 14837</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5756</t>
+          <t>0; 5034</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5994</t>
+          <t>0; 7041</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 8094</t>
+          <t>0; 8786</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5957; 20789</t>
+          <t>5687; 19893</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4294</t>
+          <t>0; 4911</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>922; 7610</t>
+          <t>923; 7608</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1821; 13407</t>
+          <t>2005; 11847</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11993; 29492</t>
+          <t>11982; 30052</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 7870</t>
+          <t>0; 7220</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1902; 10930</t>
+          <t>1936; 11164</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3338; 16075</t>
+          <t>3166; 15088</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>2538</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3431</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>5969</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2897; 13838</t>
+          <t>2915; 13304</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1845; 10723</t>
+          <t>1879; 11012</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>919; 10145</t>
+          <t>918; 9158</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 7803</t>
+          <t>0; 8909</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5307; 19006</t>
+          <t>5296; 17935</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1872; 11396</t>
+          <t>1821; 10352</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>983; 8905</t>
+          <t>980; 9495</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1243; 7504</t>
+          <t>849; 7542</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10997; 28256</t>
+          <t>10810; 27628</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4785; 17275</t>
+          <t>4830; 18177</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3295; 14743</t>
+          <t>3083; 13996</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2441; 12009</t>
+          <t>2346; 12235</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12550</t>
+          <t>13509</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>11749</t>
+          <t>12174</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24300</t>
+          <t>25684</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8013; 24500</t>
+          <t>7826; 24128</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2965; 17306</t>
+          <t>2209; 17702</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3120; 14606</t>
+          <t>3153; 13885</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4180; 24106</t>
+          <t>7114; 23621</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8852; 23925</t>
+          <t>9038; 23836</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1040; 12459</t>
+          <t>1081; 13519</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1009; 9324</t>
+          <t>1014; 9900</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7133; 18181</t>
+          <t>7884; 18807</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20904; 42759</t>
+          <t>19723; 42178</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5937; 23080</t>
+          <t>6020; 23397</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5250; 19264</t>
+          <t>6041; 19126</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13439; 35465</t>
+          <t>17256; 36735</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18095</t>
+          <t>20351</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15896</t>
+          <t>17918</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>33991</t>
+          <t>38270</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>16499; 35860</t>
+          <t>17080; 34735</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8396; 26308</t>
+          <t>8755; 27367</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12802; 31438</t>
+          <t>12236; 32803</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10993; 25901</t>
+          <t>12534; 30257</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4468; 17200</t>
+          <t>4024; 16850</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4052; 16686</t>
+          <t>4289; 16617</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3182; 14408</t>
+          <t>2333; 14056</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10545; 22680</t>
+          <t>11931; 25658</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>23060; 45797</t>
+          <t>24346; 45508</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16032; 37375</t>
+          <t>15746; 37270</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17144; 39711</t>
+          <t>16514; 39068</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>24610; 44342</t>
+          <t>28789; 50908</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24043</t>
+          <t>25621</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>16457</t>
+          <t>18513</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>40500</t>
+          <t>44135</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>21725; 41611</t>
+          <t>21620; 41457</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10948; 28672</t>
+          <t>10381; 29081</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7758; 22004</t>
+          <t>7738; 22575</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17259; 31644</t>
+          <t>18144; 34834</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12443; 29199</t>
+          <t>12912; 29295</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2030; 12064</t>
+          <t>2051; 12175</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7001; 22064</t>
+          <t>6852; 21327</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6008; 27957</t>
+          <t>12907; 25353</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>38184; 63742</t>
+          <t>38990; 65128</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15140; 34852</t>
+          <t>14318; 34873</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17793; 38074</t>
+          <t>17662; 37637</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17229; 54868</t>
+          <t>34953; 55856</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24301</t>
+          <t>25596</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>27690</t>
+          <t>29970</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>51991</t>
+          <t>55566</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>34313; 57841</t>
+          <t>33918; 57746</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>18955; 38587</t>
+          <t>19383; 40072</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11343; 27905</t>
+          <t>12150; 27275</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17678; 33488</t>
+          <t>18374; 33978</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>14969; 36125</t>
+          <t>16196; 35868</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9873; 25531</t>
+          <t>9968; 25410</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8193; 26085</t>
+          <t>8211; 26684</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>21418; 35451</t>
+          <t>22616; 39389</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>55905; 86844</t>
+          <t>54238; 85981</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>32663; 60566</t>
+          <t>32124; 58002</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23701; 47355</t>
+          <t>23375; 46256</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>42471; 62714</t>
+          <t>44739; 67198</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>83692</t>
+          <t>89995</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>88570</t>
+          <t>95820</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>172262</t>
+          <t>185815</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>113437; 157978</t>
+          <t>116127; 161980</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>56944; 93437</t>
+          <t>55218; 91308</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>51201; 83469</t>
+          <t>51915; 84355</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>62876; 101720</t>
+          <t>72487; 107672</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>73793; 112672</t>
+          <t>74356; 110814</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>31756; 58506</t>
+          <t>30856; 57667</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>33464; 60705</t>
+          <t>31237; 60482</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>70208; 108383</t>
+          <t>81023; 113973</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>198466; 259841</t>
+          <t>199435; 257911</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>95569; 139176</t>
+          <t>95606; 141689</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>91677; 132478</t>
+          <t>92622; 132714</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>144396; 201656</t>
+          <t>159961; 211854</t>
         </is>
       </c>
     </row>
